--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-historique-de-la-grossesse.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1005,7 +1005,7 @@
 </t>
   </si>
   <si>
-    <t>Informations relatives aux naissances</t>
+    <t>Période de la grossesse</t>
   </si>
   <si>
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
